--- a/outputs/Estadistica Ejercicio/Heatmap/Resumenes_Llamadas/Alcohol y drogas.xlsx
+++ b/outputs/Estadistica Ejercicio/Heatmap/Resumenes_Llamadas/Alcohol y drogas.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Intoxicación / Sobredosis / En" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Consumo De Drogas En Vía Públi" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Consumo De Alcohol En Vía Públ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Alteración Persona Drogada (Se" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Alteración Persona Alcoholizad" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tráfico De Drogas Y Estupefaci" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Asociación Delictuosa O Pandil" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">Municipio</t>
   </si>
@@ -42,39 +42,33 @@
     <t xml:space="preserve">Mineral de la Reforma</t>
   </si>
   <si>
+    <t xml:space="preserve">Tlanalapa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tula de Allende</t>
   </si>
   <si>
+    <t xml:space="preserve">Tepeji del Río de Ocampo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapotlán de Juárez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tepeapulco</t>
   </si>
   <si>
-    <t xml:space="preserve">Tlanalapa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apan</t>
   </si>
   <si>
-    <t xml:space="preserve">Tepeji del Río de Ocampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zapotlán de Juárez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Incidente</t>
   </si>
   <si>
     <t xml:space="preserve">Recuento</t>
   </si>
   <si>
-    <t xml:space="preserve">Alteración Del Orden Público Por Persona Alcoholizada (Seguridad)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consumo De Alcohol En Vía Pública (Seguridad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alteración Del Orden Público Por Persona Drogada (Seguridad)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consumo De Drogas En Vía Pública (Seguridad)</t>
   </si>
   <si>
@@ -84,6 +78,12 @@
     <t xml:space="preserve">Intoxicación Etílica (Medico)</t>
   </si>
   <si>
+    <t xml:space="preserve">Tráfico De Drogas Y Estupefacientes En Vía Pública (Seguridad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asociación Delictuosa O Pandillerismo (Seguridad)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colonia</t>
   </si>
   <si>
@@ -537,103 +537,22 @@
     <t xml:space="preserve">San Juan (Colonia)</t>
   </si>
   <si>
-    <t xml:space="preserve">La Laguna (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guadalupe Salitrería (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infonavit (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Capulines (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José El Mirador (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José Jiquilpan (Ranchería)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Candelaria (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bartolomé Tepetates (Pueblo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carros (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colonia Del Trabajo (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Pedregal (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidalgo (Zona Industrial)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Reyes (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahagún (Parque Industrial)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Y Minerales (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salvador Allende (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tepeapulco (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valle De Guadalupe (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineros (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Malinche (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Mirador (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurgentes (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Herradero (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Palma (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obrera (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loma Bonita (Ampliación)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Tulipanes (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Cides (Pueblo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tadeo De Niza (Fraccionamiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Loma (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Llano Primera Sección (Colonia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niños Héroes (Colonia)</t>
+    <t xml:space="preserve">El Arbolito (Barrio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Huixmí-Pitahayas (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuevo Hidalgo (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zona Plateada (Fraccionamiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Águilas (Colonia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada La Morena (Fraccionamiento)</t>
   </si>
 </sst>
 </file>
@@ -981,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3299</v>
+        <v>3.2482</v>
       </c>
     </row>
     <row r="3">
@@ -992,7 +911,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>6.266</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="4">
@@ -1003,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>5.5882</v>
+        <v>1.8496</v>
       </c>
     </row>
     <row r="5">
@@ -1014,7 +933,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.0397</v>
+        <v>1.3498</v>
       </c>
     </row>
     <row r="6">
@@ -1025,7 +944,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.627</v>
+        <v>1.2944</v>
       </c>
     </row>
     <row r="7">
@@ -1036,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4194</v>
+        <v>1.2259</v>
       </c>
     </row>
     <row r="8">
@@ -1047,7 +966,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2776</v>
+        <v>1.1659</v>
       </c>
     </row>
     <row r="9">
@@ -1058,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1917</v>
+        <v>1.1379</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +988,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0313</v>
+        <v>1.0497</v>
       </c>
     </row>
   </sheetData>
@@ -1096,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1165,10 +1084,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>527</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1176,10 +1095,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1187,32 +1106,32 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13">
@@ -1220,10 +1139,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>1496</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1231,10 +1150,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>730</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -1242,362 +1161,285 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>593</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>291</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>89</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
         <v>18</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>221</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C36" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C38" t="n">
-        <v>542</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
       </c>
       <c r="C40" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1630,7 +1472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -1639,7 +1481,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -1647,7 +1489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -1656,7 +1498,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1673,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -1690,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -1707,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -1724,7 +1566,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -1741,7 +1583,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1758,7 +1600,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1775,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -1792,7 +1634,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1809,7 +1651,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1826,7 +1668,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1843,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1860,7 +1702,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1877,7 +1719,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1894,7 +1736,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -1911,7 +1753,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -1928,7 +1770,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -1945,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -1962,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
@@ -1979,7 +1821,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1996,7 +1838,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -2013,7 +1855,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -2030,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -2047,7 +1889,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -2055,7 +1897,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -2064,7 +1906,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -2072,7 +1914,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>
@@ -2081,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -2089,7 +1931,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
         <v>48</v>
@@ -2098,7 +1940,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -2106,7 +1948,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
         <v>49</v>
@@ -2115,7 +1957,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -2123,7 +1965,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
         <v>50</v>
@@ -2132,7 +1974,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -2140,7 +1982,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
         <v>51</v>
@@ -2149,7 +1991,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -2157,7 +1999,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
         <v>52</v>
@@ -2166,7 +2008,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -2174,7 +2016,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
         <v>53</v>
@@ -2183,7 +2025,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -2191,7 +2033,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -2200,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -2208,7 +2050,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
         <v>55</v>
@@ -2217,7 +2059,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -2225,7 +2067,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
         <v>56</v>
@@ -2234,7 +2076,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -2242,7 +2084,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
         <v>57</v>
@@ -2251,7 +2093,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -2259,7 +2101,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
@@ -2268,7 +2110,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -2276,7 +2118,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -2285,7 +2127,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -2293,7 +2135,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
         <v>59</v>
@@ -2302,7 +2144,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -2310,7 +2152,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
         <v>60</v>
@@ -2319,7 +2161,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -2327,7 +2169,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
         <v>61</v>
@@ -2336,7 +2178,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -2344,7 +2186,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>62</v>
@@ -2353,7 +2195,7 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -2370,7 +2212,7 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
@@ -2387,7 +2229,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -2404,7 +2246,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -2421,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -2438,7 +2280,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -2455,7 +2297,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -2472,7 +2314,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -2489,7 +2331,7 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -2506,7 +2348,7 @@
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -2523,7 +2365,7 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -2540,7 +2382,7 @@
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -2557,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -2574,7 +2416,7 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -2591,7 +2433,7 @@
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -2608,7 +2450,7 @@
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -2625,7 +2467,7 @@
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -2642,7 +2484,7 @@
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -2659,7 +2501,7 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -2667,7 +2509,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
         <v>23</v>
@@ -2676,7 +2518,7 @@
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
         <v>5</v>
@@ -2684,7 +2526,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
         <v>81</v>
@@ -2693,7 +2535,7 @@
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -2701,7 +2543,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
         <v>82</v>
@@ -2710,7 +2552,7 @@
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -2746,7 +2588,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>83</v>
@@ -2755,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -2763,7 +2605,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -2772,7 +2614,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -2780,7 +2622,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -2789,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2797,7 +2639,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
@@ -2806,7 +2648,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -2814,7 +2656,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>85</v>
@@ -2823,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -2840,7 +2682,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>13</v>
@@ -2857,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
@@ -2874,7 +2716,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2891,7 +2733,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2908,7 +2750,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2925,7 +2767,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2942,7 +2784,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2959,7 +2801,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -2976,7 +2818,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
         <v>6</v>
@@ -2993,7 +2835,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
@@ -3010,7 +2852,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -3027,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -3044,7 +2886,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -3061,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -3078,7 +2920,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
@@ -3095,7 +2937,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
@@ -3103,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -3112,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -3120,7 +2962,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>94</v>
@@ -3129,7 +2971,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -3137,7 +2979,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -3146,7 +2988,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -3154,7 +2996,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
         <v>95</v>
@@ -3163,7 +3005,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -3171,7 +3013,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
         <v>63</v>
@@ -3180,7 +3022,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -3188,7 +3030,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
@@ -3197,7 +3039,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -3205,7 +3047,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
         <v>96</v>
@@ -3214,7 +3056,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -3222,7 +3064,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
@@ -3231,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -3239,7 +3081,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
@@ -3248,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -3256,7 +3098,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
         <v>99</v>
@@ -3265,7 +3107,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -3273,7 +3115,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
         <v>55</v>
@@ -3282,7 +3124,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
@@ -3290,7 +3132,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
         <v>100</v>
@@ -3299,7 +3141,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -3307,7 +3149,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
@@ -3316,7 +3158,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -3324,7 +3166,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
         <v>101</v>
@@ -3333,7 +3175,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -3341,7 +3183,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
         <v>102</v>
@@ -3350,7 +3192,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -3358,7 +3200,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
         <v>103</v>
@@ -3367,7 +3209,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -3375,7 +3217,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
         <v>52</v>
@@ -3384,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -3392,7 +3234,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
@@ -3401,7 +3243,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -3409,7 +3251,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
         <v>104</v>
@@ -3418,7 +3260,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -3426,7 +3268,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
@@ -3435,7 +3277,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
@@ -3443,7 +3285,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
         <v>105</v>
@@ -3452,7 +3294,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -3460,7 +3302,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>106</v>
@@ -3469,7 +3311,7 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -3477,7 +3319,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B45" t="s">
         <v>107</v>
@@ -3486,7 +3328,7 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -3494,7 +3336,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
         <v>108</v>
@@ -3503,7 +3345,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -3511,7 +3353,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
@@ -3520,7 +3362,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -3528,7 +3370,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B48" t="s">
         <v>110</v>
@@ -3537,7 +3379,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -3545,7 +3387,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
@@ -3554,7 +3396,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -3562,7 +3404,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B50" t="s">
         <v>112</v>
@@ -3571,7 +3413,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -3579,7 +3421,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B51" t="s">
         <v>113</v>
@@ -3588,7 +3430,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -3596,7 +3438,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
         <v>114</v>
@@ -3605,7 +3447,7 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -3613,7 +3455,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
         <v>115</v>
@@ -3622,7 +3464,7 @@
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -3639,7 +3481,7 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E54" t="n">
         <v>6</v>
@@ -3656,7 +3498,7 @@
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -3673,7 +3515,7 @@
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
@@ -3690,7 +3532,7 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -3707,7 +3549,7 @@
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -3724,7 +3566,7 @@
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -3741,7 +3583,7 @@
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -3758,7 +3600,7 @@
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -3775,7 +3617,7 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -3792,7 +3634,7 @@
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -3809,7 +3651,7 @@
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -3826,7 +3668,7 @@
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -3843,7 +3685,7 @@
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -3860,7 +3702,7 @@
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -3877,7 +3719,7 @@
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -3894,7 +3736,7 @@
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -3911,7 +3753,7 @@
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -3928,7 +3770,7 @@
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -3945,7 +3787,7 @@
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -3962,7 +3804,7 @@
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -3979,7 +3821,7 @@
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -3996,7 +3838,7 @@
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -4013,7 +3855,7 @@
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -4030,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -4038,7 +3880,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
         <v>81</v>
@@ -4047,7 +3889,7 @@
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -4055,7 +3897,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B79" t="s">
         <v>133</v>
@@ -4064,7 +3906,7 @@
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -4100,7 +3942,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -4109,7 +3951,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -4117,7 +3959,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
@@ -4126,7 +3968,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -4134,7 +3976,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>135</v>
@@ -4143,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -4151,7 +3993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
@@ -4160,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -4168,7 +4010,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>136</v>
@@ -4177,7 +4019,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -4194,7 +4036,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
@@ -4211,7 +4053,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -4228,7 +4070,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -4245,7 +4087,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -4262,7 +4104,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -4279,7 +4121,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
         <v>31</v>
@@ -4296,7 +4138,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
@@ -4313,7 +4155,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
         <v>16</v>
@@ -4330,7 +4172,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
@@ -4347,7 +4189,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
@@ -4355,7 +4197,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
         <v>141</v>
@@ -4364,7 +4206,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -4372,7 +4214,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
         <v>94</v>
@@ -4381,7 +4223,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4389,7 +4231,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>142</v>
@@ -4398,7 +4240,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4406,7 +4248,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
         <v>143</v>
@@ -4415,7 +4257,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4423,7 +4265,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>144</v>
@@ -4432,7 +4274,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4440,7 +4282,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
         <v>85</v>
@@ -4449,7 +4291,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4457,7 +4299,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
@@ -4466,7 +4308,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4474,7 +4316,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>145</v>
@@ -4483,7 +4325,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4491,7 +4333,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>146</v>
@@ -4500,7 +4342,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4508,7 +4350,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
         <v>53</v>
@@ -4517,7 +4359,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
@@ -4525,7 +4367,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
         <v>55</v>
@@ -4534,7 +4376,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -4542,7 +4384,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
         <v>52</v>
@@ -4551,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
@@ -4559,7 +4401,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
         <v>147</v>
@@ -4568,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -4576,7 +4418,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
@@ -4585,7 +4427,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -4593,7 +4435,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
         <v>56</v>
@@ -4602,7 +4444,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -4610,7 +4452,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
@@ -4619,7 +4461,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -4627,7 +4469,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
         <v>148</v>
@@ -4636,7 +4478,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -4644,7 +4486,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
         <v>149</v>
@@ -4653,7 +4495,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -4661,7 +4503,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -4670,7 +4512,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
         <v>13</v>
@@ -4678,7 +4520,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
         <v>61</v>
@@ -4687,7 +4529,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
         <v>4</v>
@@ -4695,7 +4537,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
         <v>150</v>
@@ -4704,7 +4546,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
         <v>3</v>
@@ -4712,7 +4554,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
         <v>59</v>
@@ -4721,7 +4563,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -4729,7 +4571,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
         <v>151</v>
@@ -4738,7 +4580,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -4746,7 +4588,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
         <v>152</v>
@@ -4755,7 +4597,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -4763,7 +4605,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
         <v>115</v>
@@ -4772,7 +4614,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -4780,7 +4622,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
         <v>153</v>
@@ -4789,7 +4631,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -4806,7 +4648,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
         <v>8</v>
@@ -4823,7 +4665,7 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
         <v>5</v>
@@ -4840,7 +4682,7 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
@@ -4857,7 +4699,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -4874,7 +4716,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
@@ -4891,7 +4733,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
@@ -4908,7 +4750,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -4925,7 +4767,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
@@ -4942,7 +4784,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
@@ -4950,7 +4792,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -4959,7 +4801,7 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -4967,7 +4809,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
         <v>81</v>
@@ -4976,7 +4818,7 @@
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -5012,7 +4854,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -5021,7 +4863,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
@@ -5029,7 +4871,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
@@ -5038,7 +4880,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -5046,7 +4888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>136</v>
@@ -5055,7 +4897,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -5063,7 +4905,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>155</v>
@@ -5072,7 +4914,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -5080,7 +4922,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>156</v>
@@ -5089,7 +4931,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -5097,7 +4939,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -5106,7 +4948,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -5114,7 +4956,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>157</v>
@@ -5123,7 +4965,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -5131,7 +4973,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>158</v>
@@ -5140,7 +4982,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -5148,7 +4990,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>159</v>
@@ -5157,7 +4999,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -5174,7 +5016,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>22</v>
@@ -5191,7 +5033,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>14</v>
@@ -5208,7 +5050,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -5225,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>9</v>
@@ -5242,7 +5084,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
@@ -5259,7 +5101,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>28</v>
@@ -5276,7 +5118,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
@@ -5293,7 +5135,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
@@ -5310,7 +5152,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
@@ -5327,7 +5169,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
@@ -5335,7 +5177,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -5344,7 +5186,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -5352,7 +5194,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
         <v>145</v>
@@ -5361,7 +5203,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -5369,7 +5211,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
         <v>165</v>
@@ -5378,7 +5220,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -5386,7 +5228,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -5395,7 +5237,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
@@ -5403,7 +5245,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>94</v>
@@ -5412,7 +5254,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -5420,7 +5262,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
         <v>53</v>
@@ -5429,7 +5271,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
@@ -5437,7 +5279,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
         <v>52</v>
@@ -5446,7 +5288,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
@@ -5454,7 +5296,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
@@ -5463,7 +5305,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
@@ -5471,7 +5313,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
@@ -5480,7 +5322,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
@@ -5488,7 +5330,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
@@ -5497,7 +5339,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
@@ -5505,7 +5347,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
         <v>103</v>
@@ -5514,7 +5356,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
@@ -5522,7 +5364,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
@@ -5531,7 +5373,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
         <v>4</v>
@@ -5539,7 +5381,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
         <v>23</v>
@@ -5548,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
         <v>7</v>
@@ -5556,7 +5398,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
         <v>104</v>
@@ -5565,7 +5407,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -5573,7 +5415,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
         <v>110</v>
@@ -5582,7 +5424,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
         <v>8</v>
@@ -5590,7 +5432,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
         <v>166</v>
@@ -5599,7 +5441,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E36" t="n">
         <v>7</v>
@@ -5607,7 +5449,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
@@ -5616,7 +5458,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37" t="n">
         <v>6</v>
@@ -5624,7 +5466,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
         <v>167</v>
@@ -5633,7 +5475,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
@@ -5641,7 +5483,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
         <v>168</v>
@@ -5650,7 +5492,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39" t="n">
         <v>5</v>
@@ -5658,7 +5500,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
         <v>169</v>
@@ -5667,7 +5509,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
         <v>5</v>
@@ -5675,7 +5517,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
         <v>170</v>
@@ -5684,7 +5526,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" t="n">
         <v>5</v>
@@ -5701,7 +5543,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" t="n">
         <v>11</v>
@@ -5718,7 +5560,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E43" t="n">
         <v>11</v>
@@ -5735,7 +5577,7 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44" t="n">
         <v>10</v>
@@ -5752,7 +5594,7 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45" t="n">
         <v>9</v>
@@ -5769,7 +5611,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46" t="n">
         <v>8</v>
@@ -5786,7 +5628,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47" t="n">
         <v>8</v>
@@ -5794,7 +5636,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -5803,7 +5645,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" t="n">
         <v>6</v>
@@ -5811,7 +5653,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
         <v>81</v>
@@ -5820,7 +5662,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
@@ -5828,7 +5670,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
         <v>85</v>
@@ -5837,7 +5679,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -5873,67 +5715,67 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -5941,16 +5783,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -5958,16 +5800,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -5975,16 +5817,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -5992,1004 +5834,18 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>177</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>181</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
-        <v>143</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" t="s">
-        <v>184</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" t="s">
-        <v>185</v>
-      </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" t="s">
-        <v>186</v>
-      </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" t="s">
-        <v>187</v>
-      </c>
-      <c r="C40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
-        <v>188</v>
-      </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" t="s">
-        <v>190</v>
-      </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" t="s">
-        <v>191</v>
-      </c>
-      <c r="C51" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" t="s">
-        <v>192</v>
-      </c>
-      <c r="C55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>5</v>
-      </c>
-      <c r="B57" t="s">
-        <v>50</v>
-      </c>
-      <c r="C57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>193</v>
-      </c>
-      <c r="C60" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>194</v>
-      </c>
-      <c r="C61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" t="s">
-        <v>81</v>
-      </c>
-      <c r="C62" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" t="s">
-        <v>195</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>12</v>
-      </c>
-      <c r="B66" t="s">
-        <v>196</v>
-      </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" t="s">
-        <v>197</v>
-      </c>
-      <c r="C67" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7023,818 +5879,53 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>200</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="s">
-        <v>203</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="s">
-        <v>169</v>
-      </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
-        <v>171</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" t="s">
-        <v>195</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" t="s">
-        <v>204</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
